--- a/public/excel-to-json/id192-demo.xlsx
+++ b/public/excel-to-json/id192-demo.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rain_lin/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mingliu/Desktop/Ming_Git/Tools/asus-web-tools/public/excel-to-json/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EA46B7-2F1D-0F47-AA7F-8F18DC5D3CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89C9768-F369-FE49-814D-6C09B51A5D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20260" xr2:uid="{7311D0D1-F008-D847-AD47-B02AE6D8966F}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20120" xr2:uid="{7311D0D1-F008-D847-AD47-B02AE6D8966F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="53">
   <si>
     <t>QD-OLED</t>
   </si>
@@ -120,18 +120,6 @@
   <si>
     <t>USB Hub</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ROG Strix OLED XG27ACDMS</t>
-  </si>
-  <si>
-    <t>ROG Strix OLED XG27ACDNG</t>
-  </si>
-  <si>
-    <t>ROG Strix OLED XG27AQDMES</t>
-  </si>
-  <si>
-    <t>ROG Strix OLED XG27AQDMG</t>
   </si>
   <si>
     <r>
@@ -241,12 +229,48 @@
     <t>https://rog.asus.com/monitors/27-to-31-5-inches/rog-strix-oled-xg27acdm3/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>HDR10, 
+Dolby Vision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROG Strix OLED XG27ACDMS 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROG Strix OLED XG27ACDNG 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROG Strix OLED XG27AQDMES 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROG Strix OLED XG27AQDMG 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROG Strix OLED XG27AQDMG 5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,200 cd/m²</t>
+  </si>
+  <si>
+    <t>ROG Strix OLED XG27AQDMG 6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -268,6 +292,14 @@
       <color theme="10"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -297,7 +329,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -325,6 +357,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -679,15 +720,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEAF9932-AECF-C54A-A293-27F339D4D0CC}">
-  <dimension ref="A1:AH18"/>
+  <dimension ref="A1:AH26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="31.1640625" customWidth="1"/>
     <col min="3" max="3" width="47.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="30.1640625" bestFit="1" customWidth="1"/>
@@ -723,19 +763,23 @@
         <v>13</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -763,9 +807,7 @@
       <c r="AG1" s="3"/>
     </row>
     <row r="2" spans="1:34" ht="16">
-      <c r="A2" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
@@ -774,7 +816,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="H2" s="8"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -820,8 +862,12 @@
       <c r="F3" s="3">
         <v>27</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="G3" s="3">
+        <v>27</v>
+      </c>
+      <c r="H3" s="8">
+        <v>27</v>
+      </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -868,8 +914,12 @@
       <c r="F4" s="5">
         <v>0.67291666666666672</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="G4" s="5">
+        <v>0.67291666666666672</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0.67291666666666672</v>
+      </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
@@ -911,13 +961,17 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -959,13 +1013,17 @@
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="G6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>1</v>
+      </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -1007,13 +1065,17 @@
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -1049,19 +1111,23 @@
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -1089,7 +1155,7 @@
       <c r="AG8" s="3"/>
       <c r="AH8" s="1"/>
     </row>
-    <row r="9" spans="1:34" ht="16">
+    <row r="9" spans="1:34" ht="32">
       <c r="A9" s="4" t="b">
         <v>0</v>
       </c>
@@ -1097,7 +1163,7 @@
         <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>3</v>
@@ -1106,10 +1172,14 @@
         <v>3</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -1145,19 +1215,23 @@
         <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -1187,7 +1261,7 @@
     </row>
     <row r="11" spans="1:34" ht="16">
       <c r="A11" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>6</v>
@@ -1197,7 +1271,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="8"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -1227,7 +1301,7 @@
     </row>
     <row r="12" spans="1:34" ht="16">
       <c r="A12" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>16</v>
@@ -1244,8 +1318,12 @@
       <c r="F12" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>1</v>
+      </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -1275,25 +1353,29 @@
     </row>
     <row r="13" spans="1:34" ht="16">
       <c r="A13" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -1323,25 +1405,29 @@
     </row>
     <row r="14" spans="1:34" ht="16">
       <c r="A14" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -1371,25 +1457,29 @@
     </row>
     <row r="15" spans="1:34" ht="16">
       <c r="A15" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -1425,19 +1515,23 @@
         <v>20</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -1484,8 +1578,12 @@
       <c r="F17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="G17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>1</v>
+      </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -1515,25 +1613,29 @@
     </row>
     <row r="18" spans="1:34" ht="48">
       <c r="A18" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
+        <v>41</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="I18" s="6"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
@@ -1560,11 +1662,416 @@
       <c r="AF18" s="7"/>
       <c r="AG18" s="7"/>
     </row>
+    <row r="19" spans="1:34" ht="16">
+      <c r="A19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="1"/>
+    </row>
+    <row r="20" spans="1:34" ht="16">
+      <c r="A20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="3"/>
+      <c r="AH20" s="1"/>
+    </row>
+    <row r="21" spans="1:34" ht="16">
+      <c r="A21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+      <c r="AH21" s="1"/>
+    </row>
+    <row r="22" spans="1:34" ht="16">
+      <c r="A22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+      <c r="AH22" s="1"/>
+    </row>
+    <row r="23" spans="1:34" ht="16">
+      <c r="A23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+      <c r="AH23" s="1"/>
+    </row>
+    <row r="24" spans="1:34" ht="16">
+      <c r="A24" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+      <c r="AH24" s="1"/>
+    </row>
+    <row r="25" spans="1:34" ht="16">
+      <c r="A25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="1"/>
+    </row>
+    <row r="26" spans="1:34" ht="48">
+      <c r="A26" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="6"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="6"/>
+      <c r="X26" s="7"/>
+      <c r="Y26" s="7"/>
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="7"/>
+      <c r="AB26" s="7"/>
+      <c r="AC26" s="6"/>
+      <c r="AD26" s="7"/>
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="7"/>
+      <c r="AG26" s="7"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D18" r:id="rId1" xr:uid="{B8E284F3-3063-5845-85ED-462EDFC802B9}"/>
     <hyperlink ref="E18" r:id="rId2" xr:uid="{F254E032-C98A-EA40-B7A0-59B9FF68943B}"/>
+    <hyperlink ref="D26" r:id="rId3" xr:uid="{2FF5E5CA-C171-9848-B161-8917885F41BB}"/>
+    <hyperlink ref="E26" r:id="rId4" xr:uid="{7F6DD5B2-B7BA-9D40-9CEC-851E75C015F5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/excel-to-json/id192-demo.xlsx
+++ b/public/excel-to-json/id192-demo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mingliu/Desktop/Ming_Git/Tools/asus-web-tools/public/excel-to-json/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89C9768-F369-FE49-814D-6C09B51A5D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7015945C-2934-1748-9A51-EBBD9B3B8B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20120" xr2:uid="{7311D0D1-F008-D847-AD47-B02AE6D8966F}"/>
+    <workbookView xWindow="85760" yWindow="-12000" windowWidth="23040" windowHeight="20240" xr2:uid="{7311D0D1-F008-D847-AD47-B02AE6D8966F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="64">
   <si>
     <t>QD-OLED</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Anti-Reflection</t>
-  </si>
-  <si>
-    <t>HDR10</t>
   </si>
   <si>
     <t>Display</t>
@@ -138,9 +135,6 @@
     </r>
   </si>
   <si>
-    <t>280Hz</t>
-  </si>
-  <si>
     <t>1 (FRL)</t>
   </si>
   <si>
@@ -215,10 +209,6 @@
     <t>96W</t>
   </si>
   <si>
-    <t>Learn more</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://rog.asus.com/monitors/27-to-31-5-inches/rog-strix-oled-xg27acdms/</t>
   </si>
   <si>
@@ -263,6 +253,62 @@
   </si>
   <si>
     <t>test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Learn more</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Buy now</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N/A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>280Hz&lt;br&gt;849849</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2 (FRL)&lt;br&gt;5616515</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yes&lt;br&gt;651615616</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 (DP Alt Mode)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QD-OLED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1]1 (FRL)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1]HDR10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2]1 (DP Alt Mode)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2]HDR10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3]Anti-Reflection&lt;br&gt;4849498</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rog.asus.com/monitors/27-to-31-5-inches/rog-strix-oled-xg27acdms/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -270,7 +316,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -303,6 +349,13 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -329,7 +382,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -367,6 +420,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -757,28 +813,28 @@
   <sheetData>
     <row r="1" spans="1:34" ht="16">
       <c r="A1" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>51</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -809,7 +865,7 @@
     <row r="2" spans="1:34" ht="16">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -844,11 +900,9 @@
       <c r="AG2" s="3"/>
     </row>
     <row r="3" spans="1:34" ht="16">
-      <c r="A3" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3">
         <v>26.5</v>
@@ -896,11 +950,9 @@
       <c r="AH3" s="1"/>
     </row>
     <row r="4" spans="1:34" ht="16">
-      <c r="A4" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5">
         <v>0.67291666666666672</v>
@@ -948,29 +1000,27 @@
       <c r="AH4" s="2"/>
     </row>
     <row r="5" spans="1:34" ht="16">
-      <c r="A5" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -1000,11 +1050,9 @@
       <c r="AH5" s="1"/>
     </row>
     <row r="6" spans="1:34" ht="16">
-      <c r="A6" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -1013,7 +1061,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>1</v>
@@ -1052,29 +1100,27 @@
       <c r="AH6" s="1"/>
     </row>
     <row r="7" spans="1:34" ht="16">
-      <c r="A7" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -1104,29 +1150,27 @@
       <c r="AH7" s="1"/>
     </row>
     <row r="8" spans="1:34" ht="16">
-      <c r="A8" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -1156,29 +1200,27 @@
       <c r="AH8" s="1"/>
     </row>
     <row r="9" spans="1:34" ht="32">
-      <c r="A9" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
+        <v>41</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -1208,29 +1250,27 @@
       <c r="AH9" s="1"/>
     </row>
     <row r="10" spans="1:34" ht="16">
-      <c r="A10" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -1260,11 +1300,9 @@
       <c r="AH10" s="1"/>
     </row>
     <row r="11" spans="1:34" ht="16">
-      <c r="A11" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -1300,14 +1338,12 @@
       <c r="AH11" s="1"/>
     </row>
     <row r="12" spans="1:34" ht="16">
-      <c r="A12" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>1</v>
@@ -1352,29 +1388,27 @@
       <c r="AH12" s="1"/>
     </row>
     <row r="13" spans="1:34" ht="16">
-      <c r="A13" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -1404,29 +1438,27 @@
       <c r="AH13" s="1"/>
     </row>
     <row r="14" spans="1:34" ht="16">
-      <c r="A14" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -1456,29 +1488,27 @@
       <c r="AH14" s="1"/>
     </row>
     <row r="15" spans="1:34" ht="16">
-      <c r="A15" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
@@ -1508,29 +1538,27 @@
       <c r="AH15" s="1"/>
     </row>
     <row r="16" spans="1:34" ht="16">
-      <c r="A16" s="4" t="b">
-        <v>1</v>
-      </c>
+      <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -1560,11 +1588,9 @@
       <c r="AH16" s="1"/>
     </row>
     <row r="17" spans="1:34" ht="16">
-      <c r="A17" s="4" t="b">
-        <v>1</v>
-      </c>
+      <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -1611,70 +1637,67 @@
       <c r="AG17" s="3"/>
       <c r="AH17" s="1"/>
     </row>
-    <row r="18" spans="1:34" ht="48">
-      <c r="A18" s="4" t="b">
-        <v>1</v>
-      </c>
+    <row r="18" spans="1:34" ht="16">
+      <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" s="6"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="6"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="6"/>
-      <c r="AD18" s="7"/>
-      <c r="AE18" s="6"/>
-      <c r="AF18" s="7"/>
-      <c r="AG18" s="7"/>
+        <v>49</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="3"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="3"/>
+      <c r="AH18" s="1"/>
     </row>
     <row r="19" spans="1:34" ht="16">
-      <c r="A19" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="8"/>
+        <v>15</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>1</v>
+      </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -1703,29 +1726,27 @@
       <c r="AH19" s="1"/>
     </row>
     <row r="20" spans="1:34" ht="16">
-      <c r="A20" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
@@ -1755,29 +1776,27 @@
       <c r="AH20" s="1"/>
     </row>
     <row r="21" spans="1:34" ht="16">
-      <c r="A21" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -1807,29 +1826,27 @@
       <c r="AH21" s="1"/>
     </row>
     <row r="22" spans="1:34" ht="16">
-      <c r="A22" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -1859,29 +1876,27 @@
       <c r="AH22" s="1"/>
     </row>
     <row r="23" spans="1:34" ht="16">
-      <c r="A23" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -1911,29 +1926,27 @@
       <c r="AH23" s="1"/>
     </row>
     <row r="24" spans="1:34" ht="16">
-      <c r="A24" s="4" t="b">
-        <v>1</v>
-      </c>
+      <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -1962,82 +1975,77 @@
       <c r="AG24" s="3"/>
       <c r="AH24" s="1"/>
     </row>
-    <row r="25" spans="1:34" ht="16">
+    <row r="25" spans="1:34" ht="48">
       <c r="A25" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="3"/>
-      <c r="AB25" s="3"/>
-      <c r="AC25" s="3"/>
-      <c r="AD25" s="3"/>
-      <c r="AE25" s="3"/>
-      <c r="AF25" s="3"/>
-      <c r="AG25" s="3"/>
-      <c r="AH25" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" s="6"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="6"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="7"/>
+      <c r="AB25" s="7"/>
+      <c r="AC25" s="6"/>
+      <c r="AD25" s="7"/>
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="7"/>
+      <c r="AG25" s="7"/>
     </row>
     <row r="26" spans="1:34" ht="48">
       <c r="A26" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="F26" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="7"/>
@@ -2068,11 +2076,12 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D18" r:id="rId1" xr:uid="{B8E284F3-3063-5845-85ED-462EDFC802B9}"/>
-    <hyperlink ref="E18" r:id="rId2" xr:uid="{F254E032-C98A-EA40-B7A0-59B9FF68943B}"/>
-    <hyperlink ref="D26" r:id="rId3" xr:uid="{2FF5E5CA-C171-9848-B161-8917885F41BB}"/>
-    <hyperlink ref="E26" r:id="rId4" xr:uid="{7F6DD5B2-B7BA-9D40-9CEC-851E75C015F5}"/>
+    <hyperlink ref="E25" r:id="rId1" xr:uid="{7F6DD5B2-B7BA-9D40-9CEC-851E75C015F5}"/>
+    <hyperlink ref="E26" r:id="rId2" xr:uid="{89F513D6-71F2-D548-9A1C-1FF3E3521277}"/>
+    <hyperlink ref="D25" r:id="rId3" xr:uid="{2FF5E5CA-C171-9848-B161-8917885F41BB}"/>
+    <hyperlink ref="C26" r:id="rId4" xr:uid="{E233F285-46AA-2640-B991-664F74F5876D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/public/excel-to-json/id192-demo.xlsx
+++ b/public/excel-to-json/id192-demo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mingliu/Desktop/Ming_Git/Tools/asus-web-tools/public/excel-to-json/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7015945C-2934-1748-9A51-EBBD9B3B8B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E480C62-43C6-3C48-B162-965BB15052A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="85760" yWindow="-12000" windowWidth="23040" windowHeight="20240" xr2:uid="{7311D0D1-F008-D847-AD47-B02AE6D8966F}"/>
+    <workbookView xWindow="85760" yWindow="-17540" windowWidth="23040" windowHeight="25780" xr2:uid="{7311D0D1-F008-D847-AD47-B02AE6D8966F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
   <si>
     <t>QD-OLED</t>
   </si>
@@ -55,19 +55,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I/O Ports</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Panel Size (inch)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Aspect Ratio</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Panel Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -225,33 +217,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ROG Strix OLED XG27ACDMS 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ROG Strix OLED XG27ACDNG 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ROG Strix OLED XG27AQDMES 3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ROG Strix OLED XG27AQDMG 4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ROG Strix OLED XG27AQDMG 5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,200 cd/m²</t>
   </si>
   <si>
-    <t>ROG Strix OLED XG27AQDMG 6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>test</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -309,6 +277,42 @@
   </si>
   <si>
     <t>https://rog.asus.com/monitors/27-to-31-5-inches/rog-strix-oled-xg27acdms/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;15W&lt;/b&gt;&lt;br&gt;eswfaferfaeewg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panel Type&lt;&lt;5&gt;&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 (DP Alt Mode)&lt;&lt;5&gt;&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.5&lt;&lt;5&gt;&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iojiojiotr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iojiojiotr1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iojiojiotr2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iojiojiotr3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iojiojiotr4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -382,7 +386,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -422,6 +426,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -776,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEAF9932-AECF-C54A-A293-27F339D4D0CC}">
-  <dimension ref="A1:AH26"/>
+  <dimension ref="A1:AH25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="31.1640625" customWidth="1"/>
@@ -816,25 +823,25 @@
         <v>4</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -902,10 +909,10 @@
     <row r="3" spans="1:34" ht="16">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3">
-        <v>26.5</v>
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="D3" s="3">
         <v>31.5</v>
@@ -952,7 +959,7 @@
     <row r="4" spans="1:34" ht="16">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="5">
         <v>0.67291666666666672</v>
@@ -1002,25 +1009,25 @@
     <row r="5" spans="1:34" ht="16">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -1052,7 +1059,7 @@
     <row r="6" spans="1:34" ht="16">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -1061,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>1</v>
@@ -1102,25 +1109,25 @@
     <row r="7" spans="1:34" ht="16">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -1152,25 +1159,25 @@
     <row r="8" spans="1:34" ht="16">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -1202,25 +1209,25 @@
     <row r="9" spans="1:34" ht="32">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -1252,25 +1259,25 @@
     <row r="10" spans="1:34" ht="16">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -1302,14 +1309,24 @@
     <row r="11" spans="1:34" ht="16">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>1</v>
+      </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -1340,25 +1357,25 @@
     <row r="12" spans="1:34" ht="16">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -1390,25 +1407,25 @@
     <row r="13" spans="1:34" ht="16">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -1440,25 +1457,25 @@
     <row r="14" spans="1:34" ht="16">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -1490,25 +1507,25 @@
     <row r="15" spans="1:34" ht="16">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
@@ -1540,25 +1557,25 @@
     <row r="16" spans="1:34" ht="16">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -1590,26 +1607,14 @@
     <row r="17" spans="1:34" ht="16">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>1</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="8"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -1640,14 +1645,26 @@
     <row r="18" spans="1:34" ht="16">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>1</v>
+      </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -1678,25 +1695,25 @@
     <row r="19" spans="1:34" ht="16">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -1728,25 +1745,25 @@
     <row r="20" spans="1:34" ht="16">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
@@ -1778,25 +1795,25 @@
     <row r="21" spans="1:34" ht="16">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -1828,25 +1845,23 @@
     <row r="22" spans="1:34" ht="16">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>28</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="12"/>
       <c r="E22" s="3" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -1875,28 +1890,28 @@
       <c r="AG22" s="3"/>
       <c r="AH22" s="1"/>
     </row>
-    <row r="23" spans="1:34" ht="16">
+    <row r="23" spans="1:34" ht="11" customHeight="1">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -1925,78 +1940,77 @@
       <c r="AG23" s="3"/>
       <c r="AH23" s="1"/>
     </row>
-    <row r="24" spans="1:34" ht="16">
-      <c r="A24" s="3"/>
+    <row r="24" spans="1:34" ht="48">
+      <c r="A24" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="B24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="3"/>
-      <c r="AB24" s="3"/>
-      <c r="AC24" s="3"/>
-      <c r="AD24" s="3"/>
-      <c r="AE24" s="3"/>
-      <c r="AF24" s="3"/>
-      <c r="AG24" s="3"/>
-      <c r="AH24" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I24" s="6"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="6"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="7"/>
+      <c r="AB24" s="7"/>
+      <c r="AC24" s="6"/>
+      <c r="AD24" s="7"/>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="7"/>
+      <c r="AG24" s="7"/>
     </row>
     <row r="25" spans="1:34" ht="48">
       <c r="A25" s="4" t="b">
         <v>0</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I25" s="6"/>
       <c r="J25" s="7"/>
@@ -2024,62 +2038,17 @@
       <c r="AF25" s="7"/>
       <c r="AG25" s="7"/>
     </row>
-    <row r="26" spans="1:34" ht="48">
-      <c r="A26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I26" s="6"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="6"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="6"/>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="7"/>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="7"/>
-      <c r="AB26" s="7"/>
-      <c r="AC26" s="6"/>
-      <c r="AD26" s="7"/>
-      <c r="AE26" s="6"/>
-      <c r="AF26" s="7"/>
-      <c r="AG26" s="7"/>
-    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C22:D22"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E25" r:id="rId1" xr:uid="{7F6DD5B2-B7BA-9D40-9CEC-851E75C015F5}"/>
-    <hyperlink ref="E26" r:id="rId2" xr:uid="{89F513D6-71F2-D548-9A1C-1FF3E3521277}"/>
+    <hyperlink ref="E24" r:id="rId2" xr:uid="{89F513D6-71F2-D548-9A1C-1FF3E3521277}"/>
     <hyperlink ref="D25" r:id="rId3" xr:uid="{2FF5E5CA-C171-9848-B161-8917885F41BB}"/>
-    <hyperlink ref="C26" r:id="rId4" xr:uid="{E233F285-46AA-2640-B991-664F74F5876D}"/>
+    <hyperlink ref="C24" r:id="rId4" xr:uid="{E233F285-46AA-2640-B991-664F74F5876D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
